--- a/Trắc nghiệm ôn luyện/DA Engineering/multiple_choice_sample_template_DATA_WAREHOUSING.xlsx
+++ b/Trắc nghiệm ôn luyện/DA Engineering/multiple_choice_sample_template_DATA_WAREHOUSING.xlsx
@@ -453,19 +453,19 @@
         <v>Fact Table chứa các dữ liệu số đo lường được (metrics/measures like revenue, quantity) và các khóa ngoại liên kết với các bảng chiều (Dimension Tables).</v>
       </c>
       <c r="E2" t="str">
+        <v>Mã nguồn các câu lệnh SQL dùng để tạo lập cấu trúc database của hệ thống — mã nguồn kỹ thuật</v>
+      </c>
+      <c r="F2" t="str">
         <v>Các số liệu đo lường định lượng và khóa ngoại trỏ tới các bảng chiều — số liệu đo lường và khóa liên kết</v>
       </c>
-      <c r="F2" t="str">
+      <c r="G2" t="str">
+        <v>Danh sách phân quyền đăng nhập của các nhân viên vận hành kho hàng — phân quyền nhân sự</v>
+      </c>
+      <c r="H2" t="str">
         <v>Các thuộc tính văn bản mô tả bối cảnh của đối tượng như tên, địa chỉ khách hàng — thuộc tính mô tả</v>
       </c>
-      <c r="G2" t="str">
-        <v>Mã nguồn các câu lệnh SQL dùng để tạo lập cấu trúc database của hệ thống — mã nguồn kỹ thuật</v>
-      </c>
-      <c r="H2" t="str">
-        <v>Danh sách phân quyền đăng nhập của các nhân viên vận hành kho hàng — phân quyền nhân sự</v>
-      </c>
       <c r="I2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -482,19 +482,19 @@
         <v>Dimension Table chứa các thuộc tính mô tả (như thông tin khách hàng, sản phẩm, địa lý, thời gian) dùng để lọc, phân nhóm (group by) và phân tích dữ liệu trong Fact Table.</v>
       </c>
       <c r="E3" t="str">
-        <v>Cung cấp thông tin bối cảnh chi tiết (Ai, Cái gì, Ở đâu, Khi nào) để giải nghĩa cho dữ liệu trong Fact Table — cung cấp bối cảnh phân tích</v>
+        <v>Lưu trữ tổng số tiền giao dịch lũy kế của toàn bộ hệ thống bán hàng — lưu trữ số tiền tổng</v>
       </c>
       <c r="F3" t="str">
-        <v>Lưu trữ tổng số tiền giao dịch lũy kế của toàn bộ hệ thống bán hàng — lưu trữ số tiền tổng</v>
+        <v>Tự động xóa các bản ghi dữ liệu trùng lặp khi người dùng gửi yêu cầu — dọn dẹp dữ liệu</v>
       </c>
       <c r="G3" t="str">
         <v>Mã hóa toàn bộ các bản ghi dữ liệu trước khi nạp vào hệ thống để bảo mật — mã hóa dữ liệu</v>
       </c>
       <c r="H3" t="str">
-        <v>Tự động xóa các bản ghi dữ liệu trùng lặp khi người dùng gửi yêu cầu — dọn dẹp dữ liệu</v>
+        <v>Cung cấp thông tin bối cảnh chi tiết (Ai, Cái gì, Ở đâu, Khi nào) để giải nghĩa cho dữ liệu trong Fact Table — cung cấp bối cảnh phân tích</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -511,19 +511,19 @@
         <v>ETL là quy trình tích hợp dữ liệu cơ bản: Trích xuất dữ liệu từ các nguồn (Extract), Biến đổi dữ liệu cho sạch và đúng chuẩn (Transform), rồi Nạp vào kho dữ liệu (Load).</v>
       </c>
       <c r="E4" t="str">
+        <v>Estimation - Testing - Launch — Ước lượng, Kiểm thử, Ra mắt sản phẩm phần mềm — quy trình dự án</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Entity - Table - Logic — Thực thể, Bảng dữ liệu, Logic nghiệp vụ hệ thống — cấu trúc database</v>
+      </c>
+      <c r="G4" t="str">
         <v>Extract - Transform - Load — Trích xuất, Biến đổi, Nạp dữ liệu vào kho dữ liệu — quy trình nạp dữ liệu</v>
       </c>
-      <c r="F4" t="str">
+      <c r="H4" t="str">
         <v>Enterprise - Target - License — Doanh nghiệp, Mục tiêu, Bản quyền phần mềm — quy trình doanh nghiệp</v>
       </c>
-      <c r="G4" t="str">
-        <v>Entity - Table - Logic — Thực thể, Bảng dữ liệu, Logic nghiệp vụ hệ thống — cấu trúc database</v>
-      </c>
-      <c r="H4" t="str">
-        <v>Estimation - Testing - Launch — Ước lượng, Kiểm thử, Ra mắt sản phẩm phần mềm — quy trình dự án</v>
-      </c>
       <c r="I4">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -540,19 +540,19 @@
         <v>Star Schema là mô hình đơn giản và phổ biến nhất trong DWH: 1 Fact Table ở giữa liên kết trực tiếp với các Dimension Tables qua mối quan hệ 1-n, trông giống hình ngôi sao.</v>
       </c>
       <c r="E5" t="str">
+        <v>Các bảng dữ liệu được xếp tuần tự thành một hàng dọc từ trên xuống dưới — mô hình tuyến tính</v>
+      </c>
+      <c r="F5" t="str">
         <v>Một Fact Table nằm ở trung tâm và kết nối trực tiếp với các Dimension Tables xung quanh — mô hình hình sao trực tiếp</v>
       </c>
-      <c r="F5" t="str">
+      <c r="G5" t="str">
+        <v>Toàn bộ dữ liệu của hệ thống được gộp chung vào đúng 1 bảng lớn duy nhất — mô hình phẳng</v>
+      </c>
+      <c r="H5" t="str">
         <v>Nhiều Fact Tables kết nối chéo với nhau mà không cần các Dimension Tables — mô hình Fact liên kết</v>
       </c>
-      <c r="G5" t="str">
-        <v>Các bảng dữ liệu được xếp tuần tự thành một hàng dọc từ trên xuống dưới — mô hình tuyến tính</v>
-      </c>
-      <c r="H5" t="str">
-        <v>Toàn bộ dữ liệu của hệ thống được gộp chung vào đúng 1 bảng lớn duy nhất — mô hình phẳng</v>
-      </c>
       <c r="I5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -569,19 +569,19 @@
         <v>OLTP (Online Transaction Processing) tối ưu hóa cho ghi/đọc nhanh các giao dịch đơn lẻ (như tạo đơn hàng). OLAP (Online Analytical Processing) tối ưu hóa cho truy vấn tổng hợp phức tạp trên lượng dữ liệu lớn để làm báo cáo.</v>
       </c>
       <c r="E6" t="str">
-        <v>OLTP dùng cho các giao dịch hàng ngày thời gian thực; OLAP dùng cho phân tích dữ liệu và báo cáo — giao dịch nhanh vs phân tích sâu</v>
+        <v>OLTP do khách hàng tự quản lý; còn OLAP do nhà nước quản lý bảo mật — chủ thể quản trị hệ thống</v>
       </c>
       <c r="F6" t="str">
         <v>OLTP chỉ lưu trữ được hình ảnh; còn OLAP chỉ lưu trữ được các con số — loại hình dữ liệu lưu trữ</v>
       </c>
       <c r="G6" t="str">
+        <v>OLTP dùng cho các giao dịch hàng ngày thời gian thực; OLAP dùng cho phân tích dữ liệu và báo cáo — giao dịch nhanh vs phân tích sâu</v>
+      </c>
+      <c r="H6" t="str">
         <v>OLTP chạy trên điện thoại di động; còn OLAP chỉ chạy được trên máy tính mainframe — môi trường phần cứng chạy</v>
       </c>
-      <c r="H6" t="str">
-        <v>OLTP do khách hàng tự quản lý; còn OLAP do nhà nước quản lý bảo mật — chủ thể quản trị hệ thống</v>
-      </c>
       <c r="I6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -598,19 +598,19 @@
         <v>Data Mart là một kho dữ liệu con, được thiết kế chuyên biệt cho nhu cầu sử dụng của một phòng ban hoặc một nhóm người dùng cụ thể trong doanh nghiệp.</v>
       </c>
       <c r="E7" t="str">
+        <v>Bảng danh sách toàn bộ các sản phẩm bị lỗi và phải trả lại nhà sản xuất — danh sách lỗi sản phẩm</v>
+      </c>
+      <c r="F7" t="str">
+        <v>Phần mềm dùng để tự động quét virus cho máy chủ cơ sở dữ liệu của dự án — diệt virus</v>
+      </c>
+      <c r="G7" t="str">
         <v>Một phân vùng kho dữ liệu thu nhỏ, tập trung vào một chủ đề hoặc một bộ phận cụ thể (như Tài chính, Sales) — kho dữ liệu chuyên biệt</v>
       </c>
-      <c r="F7" t="str">
+      <c r="H7" t="str">
         <v>Một siêu thị trực tuyến bán các bộ dữ liệu mẫu cho các nhà nghiên cứu khoa học — chợ bán dữ liệu</v>
       </c>
-      <c r="G7" t="str">
-        <v>Phần mềm dùng để tự động quét virus cho máy chủ cơ sở dữ liệu của dự án — diệt virus</v>
-      </c>
-      <c r="H7" t="str">
-        <v>Bảng danh sách toàn bộ các sản phẩm bị lỗi và phải trả lại nhà sản xuất — danh sách lỗi sản phẩm</v>
-      </c>
       <c r="I7">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -633,10 +633,10 @@
         <v>Chỉ duy nhất cơ sở dữ liệu Microsoft SQL Server — giới hạn nguồn dữ liệu</v>
       </c>
       <c r="G8" t="str">
+        <v>Bản vẽ thiết kế Figma của giao diện trang quản trị quản lý kho — bản vẽ UI</v>
+      </c>
+      <c r="H8" t="str">
         <v>Chỉ các file ảnh PNG/JPG chụp từ camera giám sát — nguồn dữ liệu hình ảnh</v>
-      </c>
-      <c r="H8" t="str">
-        <v>Bản vẽ thiết kế Figma của giao diện trang quản trị quản lý kho — bản vẽ UI</v>
       </c>
       <c r="I8">
         <v>1</v>
@@ -659,13 +659,13 @@
         <v>Quản lý và lưu trữ thông tin lịch sử khi các thuộc tính trong bảng chiều thay đổi theo thời gian — theo dõi biến động lịch sử</v>
       </c>
       <c r="F9" t="str">
+        <v>Tự động nén dung lượng của các bảng dữ liệu cũ đã lưu trên 5 năm — nén dữ liệu cũ</v>
+      </c>
+      <c r="G9" t="str">
+        <v>Đồng bộ hóa dữ liệu mật khẩu của người dùng khi họ đổi thông tin đăng nhập — đồng bộ mật khẩu</v>
+      </c>
+      <c r="H9" t="str">
         <v>Tăng tốc độ ghi dữ liệu của Fact Table lên nhanh gấp 10 lần — tăng tốc độ ghi dữ liệu</v>
-      </c>
-      <c r="G9" t="str">
-        <v>Tự động nén dung lượng của các bảng dữ liệu cũ đã lưu trên 5 năm — nén dữ liệu cũ</v>
-      </c>
-      <c r="H9" t="str">
-        <v>Đồng bộ hóa dữ liệu mật khẩu của người dùng khi họ đổi thông tin đăng nhập — đồng bộ mật khẩu</v>
       </c>
       <c r="I9">
         <v>1</v>
@@ -688,13 +688,13 @@
         <v>Additive: Cộng tổng được qua mọi chiều; Semi-additive: Chỉ cộng được qua một số chiều (như thời gian không cộng được); Non-additive: Không thể cộng tổng (chỉ dùng tỷ lệ) — khả năng cộng gộp số liệu</v>
       </c>
       <c r="F10" t="str">
+        <v>Additive lưu trong database; Semi-additive lưu trên file Excel; Non-additive lưu dạng text thô — hình thức lưu trữ</v>
+      </c>
+      <c r="G10" t="str">
         <v>Additive chỉ dùng cho số dương; Semi-additive dùng cho số âm; Non-additive chỉ dùng cho số thập phân — kiểu số học</v>
       </c>
-      <c r="G10" t="str">
+      <c r="H10" t="str">
         <v>Additive do DA tự tính; Semi-additive do hệ thống tự tính; Non-additive do PO nhập thủ công — chủ thể tính toán</v>
-      </c>
-      <c r="H10" t="str">
-        <v>Additive lưu trong database; Semi-additive lưu trên file Excel; Non-additive lưu dạng text thô — hình thức lưu trữ</v>
       </c>
       <c r="I10">
         <v>1</v>
@@ -714,19 +714,19 @@
         <v>Data Lake lưu trữ tất cả các dạng dữ liệu (cấu trúc, bán cấu trúc, phi cấu trúc) ở định dạng thô với chi phí rẻ. Schema chỉ được định nghĩa khi dữ liệu được đọc ra để sử dụng (Schema-on-read).</v>
       </c>
       <c r="E11" t="str">
+        <v>Data Lake bắt buộc phải sử dụng ngôn ngữ SQL để truy xuất dữ liệu chứ không hỗ trợ Python — giới hạn ngôn ngữ truy vấn</v>
+      </c>
+      <c r="F11" t="str">
+        <v>Data Lake chỉ dùng để lưu trữ dữ liệu lịch sử của các dự án đã thất bại — lưu trữ dự án cũ</v>
+      </c>
+      <c r="G11" t="str">
+        <v>Data Lake chỉ chạy được trên môi trường điện toán đám mây Microsoft Azure — giới hạn môi trường Cloud</v>
+      </c>
+      <c r="H11" t="str">
         <v>Data Lake lưu trữ dữ liệu thô chưa cấu trúc (Schema-on-read); Data Warehouse lưu trữ dữ liệu đã cấu trúc và làm sạch (Schema-on-write) — thô linh hoạt vs cấu trúc chuẩn hóa</v>
       </c>
-      <c r="F11" t="str">
-        <v>Data Lake chỉ chạy được trên môi trường điện toán đám mây Microsoft Azure — giới hạn môi trường Cloud</v>
-      </c>
-      <c r="G11" t="str">
-        <v>Data Lake bắt buộc phải sử dụng ngôn ngữ SQL để truy xuất dữ liệu chứ không hỗ trợ Python — giới hạn ngôn ngữ truy vấn</v>
-      </c>
-      <c r="H11" t="str">
-        <v>Data Lake chỉ dùng để lưu trữ dữ liệu lịch sử của các dự án đã thất bại — lưu trữ dự án cũ</v>
-      </c>
       <c r="I11">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -743,19 +743,19 @@
         <v>SCD Type 2 bảo toàn lịch sử đầy đủ. Khi có thay đổi, nó đóng bản ghi cũ (set End_Date = hiện tại, Is_Active = 0) và tạo một bản ghi mới (Start_Date = hiện tại, End_Date = NULL, Is_Active = 1).</v>
       </c>
       <c r="E12" t="str">
+        <v>Tự động xóa hàng dữ liệu cũ và di chuyển nó sang một file lưu trữ dạng CSV dự phòng — chuyển sang file CSV</v>
+      </c>
+      <c r="F12" t="str">
         <v>Tạo một hàng mới (New Row) trong bảng chiều với khóa chính mới, kèm trường thời hạn hiệu lực (Start_Date, End_Date, Is_Active) — tạo hàng mới lưu lịch sử</v>
       </c>
-      <c r="F12" t="str">
+      <c r="G12" t="str">
         <v>Ghi đè trực tiếp (Overwrite) dữ liệu mới lên dữ liệu cũ, làm mất hoàn toàn thông tin lịch sử trước đó — ghi đè mất lịch sử</v>
       </c>
-      <c r="G12" t="str">
+      <c r="H12" t="str">
         <v>Tạo thêm một cột mới (New Column) trong cùng một hàng để lưu giá trị cũ ngay cạnh giá trị mới — tạo cột lưu lịch sử</v>
       </c>
-      <c r="H12" t="str">
-        <v>Tự động xóa hàng dữ liệu cũ và di chuyển nó sang một file lưu trữ dạng CSV dự phòng — chuyển sang file CSV</v>
-      </c>
       <c r="I12">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -775,10 +775,10 @@
         <v>Áp dụng cơ chế nạp dữ liệu tăng trưởng (Incremental Load / Delta Load) bằng cách chỉ trích xuất và biến đổi dữ liệu thay đổi kể từ lần chạy cuối cùng — nạp dữ liệu tăng trưởng</v>
       </c>
       <c r="F13" t="str">
+        <v>Tắt toàn bộ các ràng buộc khóa ngoại và khóa chính trong kho dữ liệu để nạp dữ liệu nhanh hơn — tắt ràng buộc dữ liệu nguy hiểm</v>
+      </c>
+      <c r="G13" t="str">
         <v>Chạy lại toàn bộ dữ liệu từ đầu dự án (Full Load) hàng đêm để đảm bảo tuyệt đối không có sai sót xảy ra — Full Load hàng đêm nặng nề</v>
-      </c>
-      <c r="G13" t="str">
-        <v>Tắt toàn bộ các ràng buộc khóa ngoại và khóa chính trong kho dữ liệu để nạp dữ liệu nhanh hơn — tắt ràng buộc dữ liệu nguy hiểm</v>
       </c>
       <c r="H13" t="str">
         <v>Yêu cầu lập trình viên chia nhỏ dữ liệu thành các tệp tin Excel dung lượng dưới 10MB rồi tải lên bằng tay — thủ công chia nhỏ</v>
@@ -801,19 +801,19 @@
         <v>Conformed Dimension là bảng chiều duy nhất được thiết kế để dùng chung cho nhiều Data Marts/Fact Tables. Nhờ đó, khi ban giám đốc so sánh dữ liệu doanh thu (Sales Fact) và dữ liệu tồn kho (Inventory Fact) theo chiều thời gian (Date Dimension) hoặc chiều sản phẩm (Product Dimension) sẽ luôn khớp nhau.</v>
       </c>
       <c r="E14" t="str">
+        <v>Đảm bảo rằng dữ liệu trong Fact Table không bao giờ được phép chứa các giá trị số âm — ràng buộc số dương</v>
+      </c>
+      <c r="F14" t="str">
         <v>Cho phép nhiều Fact Tables khác nhau trong doanh nghiệp (như Sales, Inventory) sử dụng chung một bảng chiều chuẩn duy nhất (như Date, Customer) để đảm bảo tính nhất quán của báo cáo — đồng bộ hóa báo cáo đa chiều</v>
       </c>
-      <c r="F14" t="str">
+      <c r="G14" t="str">
         <v>Giúp tự động chuyển dịch toàn bộ dữ liệu chuỗi văn bản sang ngôn ngữ tiếng Anh — tự động dịch thuật dữ liệu</v>
       </c>
-      <c r="G14" t="str">
+      <c r="H14" t="str">
         <v>Giúp tối ưu hóa tốc độ tải trang của các dashboard PowerBI lên nhanh gấp 3 lần — tăng tốc dashboard</v>
       </c>
-      <c r="H14" t="str">
-        <v>Đảm bảo rằng dữ liệu trong Fact Table không bao giờ được phép chứa các giá trị số âm — ràng buộc số dương</v>
-      </c>
       <c r="I14">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -830,19 +830,19 @@
         <v>Staging Area giúp tách biệt quá trình trích xuất và biến đổi. Dữ liệu được gom nhanh chóng từ các nguồn OLTP vào Staging (đọc nhanh), sau đó các xử lý biến đổi nặng (Transform) sẽ chạy trên Staging để tránh làm chậm hệ thống đang vận hành trực tiếp của khách hàng.</v>
       </c>
       <c r="E15" t="str">
+        <v>Là phòng họp trực tiếp của các thành viên trong đội ngũ phân tích dữ liệu hàng ngày — phòng họp dự án</v>
+      </c>
+      <c r="F15" t="str">
+        <v>Là hệ thống máy chủ phụ dùng để chạy thử nghiệm các kịch bản kiểm thử bảo mật — máy chủ kiểm thử</v>
+      </c>
+      <c r="G15" t="str">
+        <v>Là nơi chứa các bản vẽ giao diện nháp phục vụ cho việc thiết kế báo cáo trực quan sau này — vùng lưu trữ bản vẽ</v>
+      </c>
+      <c r="H15" t="str">
         <v>Là vùng lưu trữ trung gian chứa dữ liệu thô trích xuất từ nguồn trước khi thực hiện các phép biến đổi phức tạp, tránh gây ảnh hưởng hiệu năng đến hệ thống nguồn OLTP — vùng đệm an toàn</v>
       </c>
-      <c r="F15" t="str">
-        <v>Là nơi chứa các bản vẽ giao diện nháp phục vụ cho việc thiết kế báo cáo trực quan sau này — vùng lưu trữ bản vẽ</v>
-      </c>
-      <c r="G15" t="str">
-        <v>Là phòng họp trực tiếp của các thành viên trong đội ngũ phân tích dữ liệu hàng ngày — phòng họp dự án</v>
-      </c>
-      <c r="H15" t="str">
-        <v>Là hệ thống máy chủ phụ dùng để chạy thử nghiệm các kịch bản kiểm thử bảo mật — máy chủ kiểm thử</v>
-      </c>
       <c r="I15">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -862,13 +862,13 @@
         <v>Append: Chỉ chèn thêm dữ liệu mới vào cuối bảng; Upsert: Kiểm tra nếu bản ghi đã tồn tại thì cập nhật (Update), nếu chưa tồn tại thì chèn mới (Insert) — chèn thêm vs cập nhật chèn</v>
       </c>
       <c r="F16" t="str">
-        <v>Append chỉ dùng cho bảng chiều; còn Upsert chỉ dùng cho bảng sự kiện — giới hạn phân loại bảng</v>
+        <v>Append bắt buộc phải chạy thủ công bằng tay; còn Upsert luôn chạy tự động qua API — cơ chế kích hoạt</v>
       </c>
       <c r="G16" t="str">
         <v>Append tự động mã hóa dữ liệu; còn Upsert tự động nén kích thước tệp tin nạp — cơ chế lưu trữ kỹ thuật</v>
       </c>
       <c r="H16" t="str">
-        <v>Append bắt buộc phải chạy thủ công bằng tay; còn Upsert luôn chạy tự động qua API — cơ chế kích hoạt</v>
+        <v>Append chỉ dùng cho bảng chiều; còn Upsert chỉ dùng cho bảng sự kiện — giới hạn phân loại bảng</v>
       </c>
       <c r="I16">
         <v>1</v>
@@ -888,19 +888,19 @@
         <v>Natural Key (như mã nhân viên, số CCCD) có thể bị thay đổi ở hệ thống nguồn hoặc trùng lặp khi tích hợp nhiều nguồn dữ liệu. Surrogate Key (khóa thay thế vô nghĩa, kiểu int/bigint) đảm bảo tính duy nhất, độc lập với nguồn và giúp câu lệnh JOIN chạy nhanh hơn nhiều so với JOIN qua chuỗi.</v>
       </c>
       <c r="E17" t="str">
+        <v>Vì hệ quản trị cơ sở dữ liệu kho dữ liệu không hỗ trợ lưu khóa chính kiểu chuỗi văn bản — giới hạn kỹ thuật CSDL</v>
+      </c>
+      <c r="F17" t="str">
         <v>Để tránh phụ thuộc vào sự thay đổi mã của hệ thống nguồn, đồng thời tối ưu hóa tốc độ JOIN bảng do khóa thay thế là kiểu số nguyên gọn nhẹ — độc lập nguồn và tối ưu JOIN</v>
       </c>
-      <c r="F17" t="str">
+      <c r="G17" t="str">
         <v>Để khách hàng dễ đọc hiểu và nhớ số khóa chính này khi truy xuất báo cáo — dễ nhớ khóa</v>
       </c>
-      <c r="G17" t="str">
+      <c r="H17" t="str">
         <v>Để hệ thống tự động mã hóa dữ liệu thông tin nhạy cảm của khách hàng — bảo mật thông tin</v>
       </c>
-      <c r="H17" t="str">
-        <v>Vì hệ quản trị cơ sở dữ liệu kho dữ liệu không hỗ trợ lưu khóa chính kiểu chuỗi văn bản — giới hạn kỹ thuật CSDL</v>
-      </c>
       <c r="I17">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -917,19 +917,19 @@
         <v>Degenerate Dimension là các thuộc tính định danh (như Invoice Number, Order ID) không có thuộc tính mô tả nào đi kèm nên không cần tạo bảng chiều riêng. Chúng được đặt thẳng trong Fact Table làm khóa tham chiếu giao dịch.</v>
       </c>
       <c r="E18" t="str">
+        <v>Một cột dữ liệu số tự động giảm giá trị đi 1 đơn vị sau mỗi ngày làm việc — giảm giá trị</v>
+      </c>
+      <c r="F18" t="str">
+        <v>Một bảng chiều chỉ chứa đúng 1 dòng dữ liệu duy nhất dùng để làm mẫu — bảng chiều mẫu</v>
+      </c>
+      <c r="G18" t="str">
+        <v>Một bảng chiều đã bị lỗi cấu trúc dữ liệu và không thể sử dụng để JOIN được nữa — bảng chiều lỗi</v>
+      </c>
+      <c r="H18" t="str">
         <v>Một thuộc tính chiều (như số hóa đơn, số giao dịch) được lưu trực tiếp trong Fact Table mà không cần liên kết với bảng chiều riêng biệt — chiều lưu trực tiếp</v>
       </c>
-      <c r="F18" t="str">
-        <v>Một bảng chiều đã bị lỗi cấu trúc dữ liệu và không thể sử dụng để JOIN được nữa — bảng chiều lỗi</v>
-      </c>
-      <c r="G18" t="str">
-        <v>Một bảng chiều chỉ chứa đúng 1 dòng dữ liệu duy nhất dùng để làm mẫu — bảng chiều mẫu</v>
-      </c>
-      <c r="H18" t="str">
-        <v>Một cột dữ liệu số tự động giảm giá trị đi 1 đơn vị sau mỗi ngày làm việc — giảm giá trị</v>
-      </c>
       <c r="I18">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -946,19 +946,19 @@
         <v>Đây là hai trường phái thiết kế DWH kinh điển. Inmon nhấn mạnh tính nhất quán và toàn vẹn dữ liệu toàn doanh nghiệp (Enterprise Data Warehouse - EDW ở dạng chuẩn hóa 3NF). Kimball nhấn mạnh tính thực tế, triển khai nhanh và dễ truy vấn (Dimensional Modeling kết hợp Conformed Dimensions).</v>
       </c>
       <c r="E19" t="str">
+        <v>Inmon chỉ sử dụng định dạng lưu trữ XML; còn Kimball bắt buộc sử dụng định dạng lưu trữ JSON — định dạng dữ liệu lưu</v>
+      </c>
+      <c r="F19" t="str">
         <v>Inmon hướng tiếp cận từ trên xuống (Top-down): Xây dựng kho dữ liệu tổng thể ở dạng chuẩn hóa 3NF trước, sau đó tạo các Data Marts phục vụ phòng ban; Kimball hướng tiếp cận từ dưới lên (Bottom-up): Xây dựng trực tiếp các Data Marts theo mô hình Dimensional Modeling (Star Schema) trước rồi tích hợp lại — Top-down chuẩn hóa vs Bottom-up Dimensional</v>
       </c>
-      <c r="F19" t="str">
+      <c r="G19" t="str">
+        <v>Inmon khuyên doanh nghiệp nên thuê ngoài vận hành kho dữ liệu; còn Kimball khuyên tự xây dựng đội ngũ nội bộ — phương thức quản trị nhân sự</v>
+      </c>
+      <c r="H19" t="str">
         <v>Inmon thiết kế kho dữ liệu chạy trên máy chủ Windows; còn Kimball thiết kế kho dữ liệu chạy trên máy chủ Linux — hệ điều hành máy chủ</v>
       </c>
-      <c r="G19" t="str">
-        <v>Inmon chỉ sử dụng định dạng lưu trữ XML; còn Kimball bắt buộc sử dụng định dạng lưu trữ JSON — định dạng dữ liệu lưu</v>
-      </c>
-      <c r="H19" t="str">
-        <v>Inmon khuyên doanh nghiệp nên thuê ngoài vận hành kho dữ liệu; còn Kimball khuyên tự xây dựng đội ngũ nội bộ — phương thức quản trị nhân sự</v>
-      </c>
       <c r="I19">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1004,19 +1004,19 @@
         <v>Để bảo vệ tính toàn vẹn tham chiếu trong DWH, việc để khóa ngoại NULL trong Fact Table là một bad practice vì nó phá vỡ câu lệnh INNER JOIN khi phân tích. Giải pháp chuẩn là tạo các bản ghi mặc định (ví dụ: Key -1 với mô tả "Unknown/Unregistered") trong Dimension Table để ánh xạ.</v>
       </c>
       <c r="E21" t="str">
+        <v>Tự động sinh ngẫu nhiên một mã khách hàng mới và chèn thêm một hàng mới vào bảng Customer sau mỗi giao dịch — sinh mã ngẫu nhiên</v>
+      </c>
+      <c r="F21" t="str">
         <v>Tạo một bản ghi mặc định trong bảng Customer có `customer_key = -1` (ví dụ: "Khách hàng vãng lai") và trỏ các giao dịch không xác định về khóa này — bản ghi mặc định xử lý NULL</v>
-      </c>
-      <c r="F21" t="str">
-        <v>Cho phép trường `customer_key` trong Fact Table nhận giá trị NULL đối với các giao dịch đó — cho phép NULL trong Fact</v>
       </c>
       <c r="G21" t="str">
         <v>Từ chối không nạp các giao dịch này vào kho dữ liệu để tránh làm sai lệch cấu trúc dữ liệu — lọc bỏ bản ghi thô</v>
       </c>
       <c r="H21" t="str">
-        <v>Tự động sinh ngẫu nhiên một mã khách hàng mới và chèn thêm một hàng mới vào bảng Customer sau mỗi giao dịch — sinh mã ngẫu nhiên</v>
+        <v>Cho phép trường `customer_key` trong Fact Table nhận giá trị NULL đối với các giao dịch đó — cho phép NULL trong Fact</v>
       </c>
       <c r="I21">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1033,19 +1033,19 @@
         <v>Pipelines có thể bị sập giữa chừng do mất điện, mất kết nối mạng. Một pipeline đạt tính Idempotent cho phép kỹ sư chạy lại (retry) từ đầu hoặc chạy lại cho một khoảng thời gian cụ thể (backfill) mà không lo dữ liệu bị nhân đôi (ví dụ: nhờ cơ chế tự động xóa dữ liệu cũ trước khi nạp mới hoặc sử dụng khóa duy nhất).</v>
       </c>
       <c r="E22" t="str">
+        <v>Là đường ống tự động mã hóa dữ liệu truyền tải bằng thuật toán bảo mật AES-256 — mã hóa bảo mật</v>
+      </c>
+      <c r="F22" t="str">
+        <v>Là đường ống bắt buộc phải hoàn thành việc nạp dữ liệu dưới 5 phút bất kể kích thước dữ liệu — giới hạn thời gian chạy</v>
+      </c>
+      <c r="G22" t="str">
         <v>Là đường ống dữ liệu mà khi chạy lại nhiều lần với cùng một tập dữ liệu đầu vào sẽ luôn cho ra cùng một kết quả duy nhất trong kho dữ liệu, không gây trùng lặp bản ghi — chạy lại an toàn không trùng lặp</v>
       </c>
-      <c r="F22" t="str">
+      <c r="H22" t="str">
         <v>Là đường ống tự động sửa chữa mã nguồn code Python khi phát sinh lỗi cú pháp trong quá trình chạy — tự động sửa code</v>
       </c>
-      <c r="G22" t="str">
-        <v>Là đường ống bắt buộc phải hoàn thành việc nạp dữ liệu dưới 5 phút bất kể kích thước dữ liệu — giới hạn thời gian chạy</v>
-      </c>
-      <c r="H22" t="str">
-        <v>Là đường ống tự động mã hóa dữ liệu truyền tải bằng thuật toán bảo mật AES-256 — mã hóa bảo mật</v>
-      </c>
       <c r="I22">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -1065,10 +1065,10 @@
         <v>Thiết kế mối quan hệ tự liên kết (Recursive Relationship / Self-Referencing Key) bằng cách thêm cột `manager_key` trong chính bảng Employee trỏ tới `employee_key` của người quản lý — mối quan hệ tự liên kết</v>
       </c>
       <c r="F23" t="str">
+        <v>Gộp toàn bộ thông tin của nhân viên, quản lý và giám đốc vào chung một cột dưới dạng chuỗi văn bản JSON — lưu trữ chuỗi JSON</v>
+      </c>
+      <c r="G23" t="str">
         <v>Tạo ra 3 bảng dữ liệu riêng biệt: Bảng Nhân viên, Bảng Quản lý, Bảng Giám đốc và liên kết chúng lại — phân tách bảng cứng nhắc</v>
-      </c>
-      <c r="G23" t="str">
-        <v>Gộp toàn bộ thông tin của nhân viên, quản lý và giám đốc vào chung một cột dưới dạng chuỗi văn bản JSON — lưu trữ chuỗi JSON</v>
       </c>
       <c r="H23" t="str">
         <v>Không thiết lập liên kết nào, yêu cầu người dùng tự tra cứu sơ đồ tổ chức trên file PDF bên ngoài — không liên kết hệ thống</v>
@@ -1091,19 +1091,19 @@
         <v>Bảo vệ PII (Personally Identifiable Information) là bắt buộc. Kỹ thuật De-identification tách biệt thông tin cá nhân và dữ liệu phân tích. Dữ liệu phân tích lâm sàng vẫn đầy đủ nhưng không thể liên kết ngược lại danh tính cụ thể nếu không có quyền giải mã bảng PII.</v>
       </c>
       <c r="E24" t="str">
+        <v>Không nạp bất kỳ thông tin bệnh án nào vào kho dữ liệu, chỉ lưu trữ thông tin hóa đơn viện phí — giới hạn phạm vi phân tích</v>
+      </c>
+      <c r="F24" t="str">
+        <v>Yêu cầu bác sĩ tự viết tắt tên bệnh nhân bằng các ký tự ngẫu nhiên khi nhập liệu vào hệ thống — viết tắt thủ công</v>
+      </c>
+      <c r="G24" t="str">
         <v>Tách biệt thông tin định danh cá nhân (PII - như Tên, Số điện thoại) sang một bảng riêng được mã hóa và giới hạn quyền truy cập tối đa; Fact Table chỉ chứa các mã số ID vô danh và dữ liệu bệnh án lâm sàng phục vụ phân tích chung — tách biệt dữ liệu định danh PII</v>
       </c>
-      <c r="F24" t="str">
+      <c r="H24" t="str">
         <v>Mã hóa toàn bộ kho dữ liệu bằng mật khẩu dùng chung duy nhất và cung cấp mật khẩu này cho tất cả nhân viên bệnh viện — chia sẻ mật khẩu chung</v>
       </c>
-      <c r="G24" t="str">
-        <v>Không nạp bất kỳ thông tin bệnh án nào vào kho dữ liệu, chỉ lưu trữ thông tin hóa đơn viện phí — giới hạn phạm vi phân tích</v>
-      </c>
-      <c r="H24" t="str">
-        <v>Yêu cầu bác sĩ tự viết tắt tên bệnh nhân bằng các ký tự ngẫu nhiên khi nhập liệu vào hệ thống — viết tắt thủ công</v>
-      </c>
       <c r="I24">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -1120,19 +1120,19 @@
         <v>Việc tính toán lịch tài chính (Financial Year có thể bắt đầu từ tháng 4, hoặc các ngày lễ dịch chuyển như Tết Âm lịch) bằng code SQL khi chạy báo cáo là cực kỳ phức tạp và chậm. Tạo một bảng Date Dimension vật lý được tính toán trước toàn bộ các cờ thuộc tính (cờ ngày lễ, cờ cuối tuần, cờ năm tài chính) giúp câu lệnh báo cáo chỉ cần JOIN đơn giản và chạy cực nhanh.</v>
       </c>
       <c r="E25" t="str">
+        <v>Yêu cầu lập trình viên tự viết các hàm tính toán ngày tháng phức tạp trực tiếp trong câu lệnh SELECT SQL của mỗi báo cáo — tính toán động trong SQL</v>
+      </c>
+      <c r="F25" t="str">
         <v>Xây dựng một bảng chiều Date Dimension vật lý chứa sẵn hàng chục thuộc tính được tính toán trước (như ngày trong tuần, quý tài chính, tuần tài chính, cờ ngày lễ, cờ mùa vụ) cho khoảng 20 năm — bảng chiều Date vật lý tiền tính toán</v>
       </c>
-      <c r="F25" t="str">
-        <v>Yêu cầu lập trình viên tự viết các hàm tính toán ngày tháng phức tạp trực tiếp trong câu lệnh SELECT SQL của mỗi báo cáo — tính toán động trong SQL</v>
-      </c>
       <c r="G25" t="str">
+        <v>Tạo 365 bảng dữ liệu tương ứng với 365 ngày trong năm để lưu trữ thông tin ngày tháng độc lập — phân tách bảng cực đoan</v>
+      </c>
+      <c r="H25" t="str">
         <v>Sử dụng các hàm mặc định của hệ quản trị cơ sở dữ liệu (như YEAR(), MONTH()) để tính toán thời gian khi chạy báo cáo — sử dụng hàm CSDL</v>
       </c>
-      <c r="H25" t="str">
-        <v>Tạo 365 bảng dữ liệu tương ứng với 365 ngày trong năm để lưu trữ thông tin ngày tháng độc lập — phân tách bảng cực đoan</v>
-      </c>
       <c r="I25">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1149,19 +1149,19 @@
         <v>Data Lineage trực quan hóa bản đồ đi của dữ liệu. Khi một chỉ số trên báo cáo PowerBI bị sai (ví dụ: Tổng doanh thu hiển thị âm), DA nhờ Data Lineage có thể truy ngược lại xem chỉ số này được tính từ bảng nào ở DWH, bảng đó được lấy từ file Staging nào, và file đó trích xuất từ API nguồn nào để khoanh vùng sửa lỗi.</v>
       </c>
       <c r="E26" t="str">
-        <v>Theo dõi nguồn gốc, luồng di chuyển và các phép biến đổi của dữ liệu từ hệ thống nguồn đầu vào đi qua các bảng trung gian cho đến báo cáo cuối cùng — theo dõi vòng đời dữ liệu</v>
+        <v>Quản lý danh sách các nhân viên đã thực hiện truy cập đọc dữ liệu trong ngày — lịch sử truy cập bảo mật</v>
       </c>
       <c r="F26" t="str">
         <v>Tính toán tổng số lượng máy chủ vật lý cần thiết để vận hành kho dữ liệu trong tương lai — ước lượng hạ tầng</v>
       </c>
       <c r="G26" t="str">
-        <v>Quản lý danh sách các nhân viên đã thực hiện truy cập đọc dữ liệu trong ngày — lịch sử truy cập bảo mật</v>
+        <v>Theo dõi nguồn gốc, luồng di chuyển và các phép biến đổi của dữ liệu từ hệ thống nguồn đầu vào đi qua các bảng trung gian cho đến báo cáo cuối cùng — theo dõi vòng đời dữ liệu</v>
       </c>
       <c r="H26" t="str">
         <v>Tự động tối ưu hóa tốc độ của các câu lệnh JOIN phức tạp trong cơ sở dữ liệu — tối ưu hóa câu lệnh</v>
       </c>
       <c r="I26">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
